--- a/downloads/arbeitsdateien/10_Projekte_2NF_zu_3NF.xlsx
+++ b/downloads/arbeitsdateien/10_Projekte_2NF_zu_3NF.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MITARBEITER" sheetId="1" r:id="R9b3bb760cd774427"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROJEKT" sheetId="2" r:id="R2b52a8f66ab1400e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MITARBEITER_PROJEKT" sheetId="3" r:id="Rba3b73576a874215"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MITARBEITER" sheetId="1" r:id="Rc28cf3a370714f87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROJEKT" sheetId="2" r:id="Rda995d23d05347c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MITARBEITER_PROJEKT" sheetId="3" r:id="R3b4fa1fd817247c0"/>
   </x:sheets>
 </x:workbook>
 </file>
